--- a/hardware/ThermalFlowMeter_PickAndPlace.xlsx
+++ b/hardware/ThermalFlowMeter_PickAndPlace.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="491">
   <si>
     <t>Designator</t>
   </si>
@@ -319,978 +319,981 @@
     <t>0805W8F1002T5E</t>
   </si>
   <si>
+    <t>-21.336mm</t>
+  </si>
+  <si>
+    <t>-26.035mm</t>
+  </si>
+  <si>
+    <t>-22.336mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>10kΩ ±1% 125mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>C17414</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>Basic Part</t>
+  </si>
+  <si>
+    <t>UNIQUER4</t>
+  </si>
+  <si>
+    <t>SW1</t>
+  </si>
+  <si>
+    <t>TS-1101-C-W</t>
+  </si>
+  <si>
+    <t>SW-SMD_L6.0-W3.3-LS8.0</t>
+  </si>
+  <si>
+    <t>-16.891mm</t>
+  </si>
+  <si>
+    <t>-28.194mm</t>
+  </si>
+  <si>
+    <t>-32.194mm</t>
+  </si>
+  <si>
+    <t>6*3.6*2.5mm 立贴 轻触开关</t>
+  </si>
+  <si>
+    <t>C318938</t>
+  </si>
+  <si>
+    <t>XKB Connectivity(中国星坤)</t>
+  </si>
+  <si>
+    <t>UNIQUESW1</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>U262-161N-4BVC11</t>
+  </si>
+  <si>
+    <t>USB-3.1-SMD_U262-161N-4BVC11</t>
+  </si>
+  <si>
+    <t>-13.843mm</t>
+  </si>
+  <si>
+    <t>29.337mm</t>
+  </si>
+  <si>
+    <t>-10.643mm</t>
+  </si>
+  <si>
+    <t>26.876mm</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Type-C 母 卧贴</t>
+  </si>
+  <si>
+    <t>C319148</t>
+  </si>
+  <si>
+    <t>UNIQUEUSB1</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>XL-2012SURC</t>
+  </si>
+  <si>
+    <t>LED0805-RD_RED</t>
+  </si>
+  <si>
+    <t>-20.32mm</t>
+  </si>
+  <si>
+    <t>-16.002mm</t>
+  </si>
+  <si>
+    <t>-14.902mm</t>
+  </si>
+  <si>
+    <t>C965812</t>
+  </si>
+  <si>
+    <t>XINGLIGHT(成兴光)</t>
+  </si>
+  <si>
+    <t>UNIQUELED4</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>-9.271mm</t>
+  </si>
+  <si>
+    <t>-10.371mm</t>
+  </si>
+  <si>
+    <t>UNIQUELED5</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>2.54-2*3P针</t>
+  </si>
+  <si>
+    <t>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54-1</t>
+  </si>
+  <si>
+    <t>5.588mm</t>
+  </si>
+  <si>
+    <t>-29.083mm</t>
+  </si>
+  <si>
+    <t>4.318mm</t>
+  </si>
+  <si>
+    <t>-26.543mm</t>
+  </si>
+  <si>
+    <t>间距:2.54mm 直插</t>
+  </si>
+  <si>
+    <t>C65114</t>
+  </si>
+  <si>
+    <t>BOOMELE(博穆精密)</t>
+  </si>
+  <si>
+    <t>插件,P=2.54mm</t>
+  </si>
+  <si>
+    <t>UNIQUEJ1</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>MCP25625-E/ML</t>
+  </si>
+  <si>
+    <t>QFN-28_L6.0-W6.0-P0.65-BL-EP</t>
+  </si>
+  <si>
+    <t>3.556mm</t>
+  </si>
+  <si>
+    <t>14.859mm</t>
+  </si>
+  <si>
+    <t>0.057mm</t>
+  </si>
+  <si>
+    <t>14.118mm</t>
+  </si>
+  <si>
+    <t>C481365</t>
+  </si>
+  <si>
+    <t>MICROCHIP(美国微芯)</t>
+  </si>
+  <si>
+    <t>QFN-28-EP(6x6)</t>
+  </si>
+  <si>
+    <t>UNIQUEU11</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>9.207mm</t>
+  </si>
+  <si>
+    <t>10.513mm</t>
+  </si>
+  <si>
+    <t>10.207mm</t>
+  </si>
+  <si>
+    <t>UNIQUEC21</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>9.271mm</t>
+  </si>
+  <si>
+    <t>8.382mm</t>
+  </si>
+  <si>
+    <t>10.271mm</t>
+  </si>
+  <si>
+    <t>UNIQUEC22</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>ATMEGA32U4-MU</t>
+  </si>
+  <si>
+    <t>VQFN-44_L7.0-W7.0-P0.50-BL-EP5.2</t>
+  </si>
+  <si>
+    <t>-8.255mm</t>
+  </si>
+  <si>
+    <t>-14.224mm</t>
+  </si>
+  <si>
+    <t>-5.755mm</t>
+  </si>
+  <si>
+    <t>-10.724mm</t>
+  </si>
+  <si>
+    <t>C112161</t>
+  </si>
+  <si>
+    <t>VQFN-44-EP(7x7)</t>
+  </si>
+  <si>
+    <t>UNIQUEU13</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>0805B105K500NT_C215803</t>
+  </si>
+  <si>
+    <t>-8.128mm</t>
+  </si>
+  <si>
+    <t>-6.604mm</t>
+  </si>
+  <si>
+    <t>-7.128mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>1uF ±10% 50V</t>
+  </si>
+  <si>
+    <t>C215803</t>
+  </si>
+  <si>
+    <t>0805B105K500NT</t>
+  </si>
+  <si>
+    <t>UNIQUEC28</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>-12.065mm</t>
+  </si>
+  <si>
+    <t>-13.065mm</t>
+  </si>
+  <si>
+    <t>UNIQUEC29</t>
+  </si>
+  <si>
+    <t>SW2</t>
+  </si>
+  <si>
+    <t>SMQS-04R-TP</t>
+  </si>
+  <si>
+    <t>SW-TH_8P-P2.54_SMQS-04R-TP</t>
+  </si>
+  <si>
+    <t>-6.096mm</t>
+  </si>
+  <si>
+    <t>-28.448mm</t>
+  </si>
+  <si>
+    <t>-2.286mm</t>
+  </si>
+  <si>
+    <t>-24.638mm</t>
+  </si>
+  <si>
+    <t>间距2.54mm 平拨,凸起式4位拨码开关</t>
+  </si>
+  <si>
+    <t>C5299505</t>
+  </si>
+  <si>
+    <t>SM Switch</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>UNIQUEU14</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>MF-SMDF050-2</t>
+  </si>
+  <si>
+    <t>F2018</t>
+  </si>
+  <si>
     <t>-19.812mm</t>
   </si>
   <si>
-    <t>-27.178mm</t>
-  </si>
-  <si>
-    <t>-28.178mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>10kΩ ±1% 125mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>C17414</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>Basic Part</t>
-  </si>
-  <si>
-    <t>UNIQUER4</t>
-  </si>
-  <si>
-    <t>SW1</t>
-  </si>
-  <si>
-    <t>TS-1101-C-W</t>
-  </si>
-  <si>
-    <t>SW-SMD_L6.0-W3.3-LS8.0</t>
-  </si>
-  <si>
-    <t>-28.194mm</t>
-  </si>
-  <si>
-    <t>-32.194mm</t>
-  </si>
-  <si>
-    <t>6*3.6*2.5mm 立贴 轻触开关</t>
-  </si>
-  <si>
-    <t>C318938</t>
-  </si>
-  <si>
-    <t>XKB Connectivity(中国星坤)</t>
-  </si>
-  <si>
-    <t>UNIQUESW1</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>U262-161N-4BVC11</t>
-  </si>
-  <si>
-    <t>USB-3.1-SMD_U262-161N-4BVC11</t>
-  </si>
-  <si>
-    <t>-13.843mm</t>
-  </si>
-  <si>
-    <t>29.337mm</t>
-  </si>
-  <si>
-    <t>-10.643mm</t>
-  </si>
-  <si>
-    <t>26.876mm</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Type-C 母 卧贴</t>
-  </si>
-  <si>
-    <t>C319148</t>
-  </si>
-  <si>
-    <t>UNIQUEUSB1</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>XL-2012SURC</t>
-  </si>
-  <si>
-    <t>LED0805-RD_RED</t>
-  </si>
-  <si>
-    <t>-19.939mm</t>
-  </si>
-  <si>
-    <t>-16.002mm</t>
-  </si>
-  <si>
-    <t>-14.902mm</t>
-  </si>
-  <si>
-    <t>C965812</t>
-  </si>
-  <si>
-    <t>XINGLIGHT(成兴光)</t>
-  </si>
-  <si>
-    <t>UNIQUELED4</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>-9.144mm</t>
-  </si>
-  <si>
-    <t>-10.244mm</t>
-  </si>
-  <si>
-    <t>UNIQUELED5</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>2.54-2*3P针</t>
-  </si>
-  <si>
-    <t>HDR-TH_6P-P2.54-V-M-R2-C3-S2.54-1</t>
-  </si>
-  <si>
-    <t>5.588mm</t>
-  </si>
-  <si>
-    <t>-29.083mm</t>
-  </si>
-  <si>
-    <t>4.318mm</t>
-  </si>
-  <si>
-    <t>-26.543mm</t>
-  </si>
-  <si>
-    <t>间距:2.54mm 直插</t>
-  </si>
-  <si>
-    <t>C65114</t>
-  </si>
-  <si>
-    <t>BOOMELE(博穆精密)</t>
-  </si>
-  <si>
-    <t>插件,P=2.54mm</t>
-  </si>
-  <si>
-    <t>UNIQUEJ1</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>MCP25625-E/ML</t>
-  </si>
-  <si>
-    <t>QFN-28_L6.0-W6.0-P0.65-BL-EP</t>
-  </si>
-  <si>
-    <t>3.556mm</t>
-  </si>
-  <si>
-    <t>14.859mm</t>
-  </si>
-  <si>
-    <t>0.057mm</t>
-  </si>
-  <si>
-    <t>14.118mm</t>
-  </si>
-  <si>
-    <t>C481365</t>
-  </si>
-  <si>
-    <t>MICROCHIP(美国微芯)</t>
-  </si>
-  <si>
-    <t>QFN-28-EP(6x6)</t>
-  </si>
-  <si>
-    <t>UNIQUEU11</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>9.207mm</t>
-  </si>
-  <si>
-    <t>10.513mm</t>
-  </si>
-  <si>
-    <t>10.207mm</t>
-  </si>
-  <si>
-    <t>UNIQUEC21</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>9.271mm</t>
-  </si>
-  <si>
-    <t>8.382mm</t>
-  </si>
-  <si>
-    <t>10.271mm</t>
-  </si>
-  <si>
-    <t>UNIQUEC22</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>ATMEGA32U4-MU</t>
-  </si>
-  <si>
-    <t>VQFN-44_L7.0-W7.0-P0.50-BL-EP5.2</t>
-  </si>
-  <si>
-    <t>-8.255mm</t>
-  </si>
-  <si>
-    <t>-14.224mm</t>
-  </si>
-  <si>
-    <t>-5.755mm</t>
-  </si>
-  <si>
-    <t>-10.724mm</t>
-  </si>
-  <si>
-    <t>C112161</t>
-  </si>
-  <si>
-    <t>VQFN-44-EP(7x7)</t>
-  </si>
-  <si>
-    <t>UNIQUEU13</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>0805B105K500NT_C215803</t>
-  </si>
-  <si>
-    <t>-8.128mm</t>
-  </si>
-  <si>
-    <t>-6.604mm</t>
-  </si>
-  <si>
-    <t>-7.128mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>1uF ±10% 50V</t>
-  </si>
-  <si>
-    <t>C215803</t>
-  </si>
-  <si>
-    <t>0805B105K500NT</t>
-  </si>
-  <si>
-    <t>UNIQUEC28</t>
-  </si>
-  <si>
-    <t>C14</t>
+    <t>17.018mm</t>
+  </si>
+  <si>
+    <t>19.65mm</t>
+  </si>
+  <si>
+    <t>60V 550mA 2018自恢复</t>
+  </si>
+  <si>
+    <t>C210839</t>
+  </si>
+  <si>
+    <t>BOURNS</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>UNIQUEF1</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>0805W8F220JT5E</t>
+  </si>
+  <si>
+    <t>-14.71mm</t>
+  </si>
+  <si>
+    <t>19.375mm</t>
+  </si>
+  <si>
+    <t>20.375mm</t>
+  </si>
+  <si>
+    <t>22Ω</t>
+  </si>
+  <si>
+    <t>22Ω ±1% 125mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>C17561</t>
+  </si>
+  <si>
+    <t>UNIQUER17</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>19.431mm</t>
+  </si>
+  <si>
+    <t>20.431mm</t>
+  </si>
+  <si>
+    <t>UNIQUER18</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>CL21A106KOQNNNE</t>
+  </si>
+  <si>
+    <t>-22.225mm</t>
+  </si>
+  <si>
+    <t>23.622mm</t>
+  </si>
+  <si>
+    <t>22.622mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>10uF ±10% 16V</t>
+  </si>
+  <si>
+    <t>C1713</t>
+  </si>
+  <si>
+    <t>SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>UNIQUEC25</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>CG0603MLC-05E</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>-11.557mm</t>
+  </si>
+  <si>
+    <t>25.019mm</t>
+  </si>
+  <si>
+    <t>-10.804mm</t>
+  </si>
+  <si>
+    <t>钳位电压30V 0603压敏电阻</t>
+  </si>
+  <si>
+    <t>C840634</t>
+  </si>
+  <si>
+    <t>0603</t>
+  </si>
+  <si>
+    <t>UNIQUER19</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>-12.043mm</t>
+  </si>
+  <si>
+    <t>23.153mm</t>
+  </si>
+  <si>
+    <t>-11.289mm</t>
+  </si>
+  <si>
+    <t>UNIQUER20</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>7.957mm</t>
+  </si>
+  <si>
+    <t>22.432mm</t>
+  </si>
+  <si>
+    <t>8.957mm</t>
+  </si>
+  <si>
+    <t>UNIQUEC27</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>CL21A475KAQNNNE</t>
+  </si>
+  <si>
+    <t>9.779mm</t>
+  </si>
+  <si>
+    <t>25.781mm</t>
+  </si>
+  <si>
+    <t>24.781mm</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>4.7uF ±10% 25V</t>
+  </si>
+  <si>
+    <t>C1779</t>
+  </si>
+  <si>
+    <t>UNIQUEC30</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>7.045mm</t>
+  </si>
+  <si>
+    <t>25.851mm</t>
+  </si>
+  <si>
+    <t>24.851mm</t>
+  </si>
+  <si>
+    <t>UNIQUEC31</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C3225X7R1C156MT000N</t>
+  </si>
+  <si>
+    <t>C1210</t>
+  </si>
+  <si>
+    <t>-2.718mm</t>
+  </si>
+  <si>
+    <t>25.724mm</t>
+  </si>
+  <si>
+    <t>24.207mm</t>
+  </si>
+  <si>
+    <t>15uF</t>
+  </si>
+  <si>
+    <t>15uF ±20% 16V</t>
+  </si>
+  <si>
+    <t>C694469</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>1210</t>
+  </si>
+  <si>
+    <t>UNIQUEC33</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SS14_C2986110</t>
+  </si>
+  <si>
+    <t>SMA_L4.3-W2.6-LS5.1-RD</t>
+  </si>
+  <si>
+    <t>-6.772mm</t>
+  </si>
+  <si>
+    <t>16.591mm</t>
+  </si>
+  <si>
+    <t>14.391mm</t>
+  </si>
+  <si>
+    <t>SS14</t>
+  </si>
+  <si>
+    <t>电压:40V 电流:1A</t>
+  </si>
+  <si>
+    <t>C2986110</t>
+  </si>
+  <si>
+    <t>GOODWORK(固得沃克)</t>
+  </si>
+  <si>
+    <t>SMA(DO-214AC)</t>
+  </si>
+  <si>
+    <t>UNIQUED1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>-12.36mm</t>
+  </si>
+  <si>
+    <t>14.427mm</t>
+  </si>
+  <si>
+    <t>-10.16mm</t>
+  </si>
+  <si>
+    <t>UNIQUED2</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>CD32YP0302-101M</t>
+  </si>
+  <si>
+    <t>IND-SMD_L3.5-W3.0_SLF0302</t>
+  </si>
+  <si>
+    <t>-2.698mm</t>
+  </si>
+  <si>
+    <t>31.069mm</t>
+  </si>
+  <si>
+    <t>-3.823mm</t>
+  </si>
+  <si>
+    <t>100uH</t>
+  </si>
+  <si>
+    <t>100uH ±20%</t>
+  </si>
+  <si>
+    <t>C492265</t>
+  </si>
+  <si>
+    <t>YJYCOIN(益嘉源)</t>
+  </si>
+  <si>
+    <t>SMD,3.5x3x2.1mm</t>
+  </si>
+  <si>
+    <t>UNIQUEL1</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>0805W8F1001T5E</t>
+  </si>
+  <si>
+    <t>-21.844mm</t>
+  </si>
+  <si>
+    <t>-20.844mm</t>
+  </si>
+  <si>
+    <t>1kΩ</t>
+  </si>
+  <si>
+    <t>1kΩ ±1% 125mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>C17513</t>
+  </si>
+  <si>
+    <t>UNIQUER12</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>-4.572mm</t>
+  </si>
+  <si>
+    <t>-5.572mm</t>
+  </si>
+  <si>
+    <t>UNIQUER13</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>RMC08055.1K5%N</t>
+  </si>
+  <si>
+    <t>-16.869mm</t>
+  </si>
+  <si>
+    <t>24.296mm</t>
+  </si>
+  <si>
+    <t>-15.869mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>5.1kΩ ±5% 125mW</t>
+  </si>
+  <si>
+    <t>C269736</t>
+  </si>
+  <si>
+    <t>Tyohm(幸亚电阻)</t>
+  </si>
+  <si>
+    <t>UNIQUER14</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>-7.09mm</t>
+  </si>
+  <si>
+    <t>31.027mm</t>
+  </si>
+  <si>
+    <t>30.027mm</t>
+  </si>
+  <si>
+    <t>UNIQUER15</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>1.524mm</t>
+  </si>
+  <si>
+    <t>8.509mm</t>
+  </si>
+  <si>
+    <t>2.524mm</t>
+  </si>
+  <si>
+    <t>UNIQUER16</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>AC0805FR-07332KL</t>
+  </si>
+  <si>
+    <t>3.302mm</t>
+  </si>
+  <si>
+    <t>22.479mm</t>
+  </si>
+  <si>
+    <t>2.302mm</t>
+  </si>
+  <si>
+    <t>332kΩ</t>
+  </si>
+  <si>
+    <t>厚膜电阻 332kΩ ±1% 125mW</t>
+  </si>
+  <si>
+    <t>C228750</t>
+  </si>
+  <si>
+    <t>YAGEO(国巨)</t>
+  </si>
+  <si>
+    <t>UNIQUER22</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>0805W8F9532T5E</t>
+  </si>
+  <si>
+    <t>-5.969mm</t>
+  </si>
+  <si>
+    <t>22.606mm</t>
+  </si>
+  <si>
+    <t>21.606mm</t>
+  </si>
+  <si>
+    <t>95.3kΩ</t>
+  </si>
+  <si>
+    <t>95.3kΩ ±1% 125mW 厚膜电阻</t>
+  </si>
+  <si>
+    <t>C17873</t>
+  </si>
+  <si>
+    <t>UNIQUER23</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>CR0805-FX-2212ELF</t>
+  </si>
+  <si>
+    <t>-1.143mm</t>
+  </si>
+  <si>
+    <t>21.336mm</t>
+  </si>
+  <si>
+    <t>-0.143mm</t>
+  </si>
+  <si>
+    <t>22.1kΩ</t>
+  </si>
+  <si>
+    <t>厚膜电阻 22.1kΩ ±1% 125mW</t>
+  </si>
+  <si>
+    <t>C204311</t>
+  </si>
+  <si>
+    <t>UNIQUER24</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>TPS560430XDBVR</t>
+  </si>
+  <si>
+    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
+  </si>
+  <si>
+    <t>25.654mm</t>
+  </si>
+  <si>
+    <t>0.121mm</t>
+  </si>
+  <si>
+    <t>26.604mm</t>
+  </si>
+  <si>
+    <t>C524782</t>
+  </si>
+  <si>
+    <t>TI(德州仪器)</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>UNIQUEU16</t>
+  </si>
+  <si>
+    <t>X1</t>
+  </si>
+  <si>
+    <t>CSTNE8M00GH5C000R0</t>
+  </si>
+  <si>
+    <t>OSC-SMD_3P-L3.2-W1.3-P1.20-L</t>
+  </si>
+  <si>
+    <t>-17.201mm</t>
+  </si>
+  <si>
+    <t>8MHz</t>
+  </si>
+  <si>
+    <t>8MHz ±0.07% 内置负载电容:33pF</t>
+  </si>
+  <si>
+    <t>C341525</t>
+  </si>
+  <si>
+    <t>muRata(村田)</t>
+  </si>
+  <si>
+    <t>SMD3213-3P</t>
+  </si>
+  <si>
+    <t>UNIQUEX1</t>
+  </si>
+  <si>
+    <t>X2</t>
+  </si>
+  <si>
+    <t>8.255mm</t>
+  </si>
+  <si>
+    <t>18.923mm</t>
+  </si>
+  <si>
+    <t>9.454mm</t>
+  </si>
+  <si>
+    <t>UNIQUEX3</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>MX128-5.0-04P-GN01-Cu-Y-A</t>
+  </si>
+  <si>
+    <t>CONN-TH_4P-MX128-5.0-04P-GN01-CU-Y-A</t>
+  </si>
+  <si>
+    <t>16.315mm</t>
+  </si>
+  <si>
+    <t>18.288mm</t>
+  </si>
+  <si>
+    <t>10.788mm</t>
+  </si>
+  <si>
+    <t>1x4P 5mm 直插 排数:1 每排P数:4</t>
+  </si>
+  <si>
+    <t>C5290369</t>
+  </si>
+  <si>
+    <t>MAX(迈旭)</t>
+  </si>
+  <si>
+    <t>插件,P=5mm</t>
+  </si>
+  <si>
+    <t>gge1</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>31.242mm</t>
+  </si>
+  <si>
+    <t>6.309mm</t>
+  </si>
+  <si>
+    <t>UNIQUED2_1</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>MX128-5.0-06P-GN01-Cu-Y-A</t>
+  </si>
+  <si>
+    <t>CONN-TH_6P-P5.00_MX128-5.0-06P-GN01-CU-Y-A</t>
   </si>
   <si>
     <t>-12.192mm</t>
   </si>
   <si>
-    <t>-20.32mm</t>
-  </si>
-  <si>
-    <t>-13.192mm</t>
-  </si>
-  <si>
-    <t>UNIQUEC29</t>
-  </si>
-  <si>
-    <t>SW2</t>
-  </si>
-  <si>
-    <t>SMQS-04R-TP</t>
-  </si>
-  <si>
-    <t>SW-TH_8P-P2.54_SMQS-04R-TP</t>
-  </si>
-  <si>
-    <t>-6.096mm</t>
-  </si>
-  <si>
-    <t>-28.448mm</t>
-  </si>
-  <si>
-    <t>-2.286mm</t>
-  </si>
-  <si>
-    <t>-24.638mm</t>
-  </si>
-  <si>
-    <t>间距2.54mm 平拨,凸起式4位拨码开关</t>
-  </si>
-  <si>
-    <t>C5299505</t>
-  </si>
-  <si>
-    <t>SM Switch</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>UNIQUEU14</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>MF-SMDF050-2</t>
-  </si>
-  <si>
-    <t>F2018</t>
-  </si>
-  <si>
-    <t>17.018mm</t>
-  </si>
-  <si>
-    <t>19.65mm</t>
-  </si>
-  <si>
-    <t>60V 550mA 2018自恢复</t>
-  </si>
-  <si>
-    <t>C210839</t>
-  </si>
-  <si>
-    <t>BOURNS</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>UNIQUEF1</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>0805W8F220JT5E</t>
-  </si>
-  <si>
-    <t>-14.71mm</t>
-  </si>
-  <si>
-    <t>19.375mm</t>
-  </si>
-  <si>
-    <t>20.375mm</t>
-  </si>
-  <si>
-    <t>22Ω</t>
-  </si>
-  <si>
-    <t>22Ω ±1% 125mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>C17561</t>
-  </si>
-  <si>
-    <t>UNIQUER17</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>-12.065mm</t>
-  </si>
-  <si>
-    <t>19.431mm</t>
-  </si>
-  <si>
-    <t>20.431mm</t>
-  </si>
-  <si>
-    <t>UNIQUER18</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>CL21A106KOQNNNE</t>
-  </si>
-  <si>
-    <t>-22.225mm</t>
-  </si>
-  <si>
-    <t>23.622mm</t>
-  </si>
-  <si>
-    <t>22.622mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>10uF ±10% 16V</t>
-  </si>
-  <si>
-    <t>C1713</t>
-  </si>
-  <si>
-    <t>SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>UNIQUEC25</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>CG0603MLC-05E</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>-11.557mm</t>
-  </si>
-  <si>
-    <t>25.019mm</t>
-  </si>
-  <si>
-    <t>-10.804mm</t>
-  </si>
-  <si>
-    <t>钳位电压30V 0603压敏电阻</t>
-  </si>
-  <si>
-    <t>C840634</t>
-  </si>
-  <si>
-    <t>0603</t>
-  </si>
-  <si>
-    <t>UNIQUER19</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>-12.043mm</t>
-  </si>
-  <si>
-    <t>23.153mm</t>
-  </si>
-  <si>
-    <t>-11.289mm</t>
-  </si>
-  <si>
-    <t>UNIQUER20</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>7.957mm</t>
-  </si>
-  <si>
-    <t>22.432mm</t>
-  </si>
-  <si>
-    <t>8.957mm</t>
-  </si>
-  <si>
-    <t>UNIQUEC27</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>CL21A475KAQNNNE</t>
-  </si>
-  <si>
-    <t>9.779mm</t>
-  </si>
-  <si>
-    <t>25.781mm</t>
-  </si>
-  <si>
-    <t>24.781mm</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>4.7uF ±10% 25V</t>
-  </si>
-  <si>
-    <t>C1779</t>
-  </si>
-  <si>
-    <t>UNIQUEC30</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>7.045mm</t>
-  </si>
-  <si>
-    <t>25.851mm</t>
-  </si>
-  <si>
-    <t>24.851mm</t>
-  </si>
-  <si>
-    <t>UNIQUEC31</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>C3225X7R1C156MT000N</t>
-  </si>
-  <si>
-    <t>C1210</t>
-  </si>
-  <si>
-    <t>-2.718mm</t>
-  </si>
-  <si>
-    <t>25.724mm</t>
-  </si>
-  <si>
-    <t>24.207mm</t>
-  </si>
-  <si>
-    <t>15uF</t>
-  </si>
-  <si>
-    <t>15uF ±20% 16V</t>
-  </si>
-  <si>
-    <t>C694469</t>
-  </si>
-  <si>
-    <t>TDK</t>
-  </si>
-  <si>
-    <t>1210</t>
-  </si>
-  <si>
-    <t>UNIQUEC33</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>SS14_C2986110</t>
-  </si>
-  <si>
-    <t>SMA_L4.3-W2.6-LS5.1-RD</t>
-  </si>
-  <si>
-    <t>-6.772mm</t>
-  </si>
-  <si>
-    <t>16.591mm</t>
-  </si>
-  <si>
-    <t>14.391mm</t>
-  </si>
-  <si>
-    <t>SS14</t>
-  </si>
-  <si>
-    <t>电压:40V 电流:1A</t>
-  </si>
-  <si>
-    <t>C2986110</t>
-  </si>
-  <si>
-    <t>GOODWORK(固得沃克)</t>
-  </si>
-  <si>
-    <t>SMA(DO-214AC)</t>
-  </si>
-  <si>
-    <t>UNIQUED1</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>-12.36mm</t>
-  </si>
-  <si>
-    <t>14.427mm</t>
-  </si>
-  <si>
-    <t>-10.16mm</t>
-  </si>
-  <si>
-    <t>UNIQUED2</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>CD32YP0302-101M</t>
-  </si>
-  <si>
-    <t>IND-SMD_L3.5-W3.0_SLF0302</t>
-  </si>
-  <si>
-    <t>-2.698mm</t>
-  </si>
-  <si>
-    <t>31.069mm</t>
-  </si>
-  <si>
-    <t>-3.823mm</t>
-  </si>
-  <si>
-    <t>100uH</t>
-  </si>
-  <si>
-    <t>100uH ±20%</t>
-  </si>
-  <si>
-    <t>C492265</t>
-  </si>
-  <si>
-    <t>YJYCOIN(益嘉源)</t>
-  </si>
-  <si>
-    <t>SMD,3.5x3x2.1mm</t>
-  </si>
-  <si>
-    <t>UNIQUEL1</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>0805W8F1001T5E</t>
-  </si>
-  <si>
-    <t>-21.844mm</t>
-  </si>
-  <si>
-    <t>-20.844mm</t>
-  </si>
-  <si>
-    <t>1kΩ</t>
-  </si>
-  <si>
-    <t>1kΩ ±1% 125mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>C17513</t>
-  </si>
-  <si>
-    <t>UNIQUER12</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>-4.572mm</t>
-  </si>
-  <si>
-    <t>-5.572mm</t>
-  </si>
-  <si>
-    <t>UNIQUER13</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>RMC08055.1K5%N</t>
-  </si>
-  <si>
-    <t>-16.869mm</t>
-  </si>
-  <si>
-    <t>24.296mm</t>
-  </si>
-  <si>
-    <t>-15.869mm</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>5.1kΩ ±5% 125mW</t>
-  </si>
-  <si>
-    <t>C269736</t>
-  </si>
-  <si>
-    <t>Tyohm(幸亚电阻)</t>
-  </si>
-  <si>
-    <t>UNIQUER14</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>-7.09mm</t>
-  </si>
-  <si>
-    <t>31.027mm</t>
-  </si>
-  <si>
-    <t>30.027mm</t>
-  </si>
-  <si>
-    <t>UNIQUER15</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>1.524mm</t>
-  </si>
-  <si>
-    <t>8.509mm</t>
-  </si>
-  <si>
-    <t>2.524mm</t>
-  </si>
-  <si>
-    <t>UNIQUER16</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>AC0805FR-07332KL</t>
-  </si>
-  <si>
-    <t>3.302mm</t>
-  </si>
-  <si>
-    <t>22.479mm</t>
-  </si>
-  <si>
-    <t>2.302mm</t>
-  </si>
-  <si>
-    <t>332kΩ</t>
-  </si>
-  <si>
-    <t>厚膜电阻 332kΩ ±1% 125mW</t>
-  </si>
-  <si>
-    <t>C228750</t>
-  </si>
-  <si>
-    <t>YAGEO(国巨)</t>
-  </si>
-  <si>
-    <t>UNIQUER22</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>0805W8F9532T5E</t>
-  </si>
-  <si>
-    <t>-5.969mm</t>
-  </si>
-  <si>
-    <t>22.606mm</t>
-  </si>
-  <si>
-    <t>21.606mm</t>
-  </si>
-  <si>
-    <t>95.3kΩ</t>
-  </si>
-  <si>
-    <t>95.3kΩ ±1% 125mW 厚膜电阻</t>
-  </si>
-  <si>
-    <t>C17873</t>
-  </si>
-  <si>
-    <t>UNIQUER23</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>CR0805-FX-2212ELF</t>
-  </si>
-  <si>
-    <t>-1.143mm</t>
-  </si>
-  <si>
-    <t>21.336mm</t>
-  </si>
-  <si>
-    <t>-0.143mm</t>
-  </si>
-  <si>
-    <t>22.1kΩ</t>
-  </si>
-  <si>
-    <t>厚膜电阻 22.1kΩ ±1% 125mW</t>
-  </si>
-  <si>
-    <t>C204311</t>
-  </si>
-  <si>
-    <t>UNIQUER24</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>TPS560430XDBVR</t>
-  </si>
-  <si>
-    <t>SOT-23-6_L2.9-W1.6-P0.95-LS2.8-BL</t>
-  </si>
-  <si>
-    <t>25.654mm</t>
-  </si>
-  <si>
-    <t>0.121mm</t>
-  </si>
-  <si>
-    <t>26.604mm</t>
-  </si>
-  <si>
-    <t>C524782</t>
-  </si>
-  <si>
-    <t>TI(德州仪器)</t>
-  </si>
-  <si>
-    <t>SOT-23-6</t>
-  </si>
-  <si>
-    <t>UNIQUEU16</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>CSTNE8M00GH5C000R0</t>
-  </si>
-  <si>
-    <t>OSC-SMD_3P-L3.2-W1.3-P1.20-L</t>
-  </si>
-  <si>
-    <t>-17.201mm</t>
-  </si>
-  <si>
-    <t>8MHz</t>
-  </si>
-  <si>
-    <t>8MHz ±0.07% 内置负载电容:33pF</t>
-  </si>
-  <si>
-    <t>C341525</t>
-  </si>
-  <si>
-    <t>muRata(村田)</t>
-  </si>
-  <si>
-    <t>SMD3213-3P</t>
-  </si>
-  <si>
-    <t>UNIQUEX1</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>8.255mm</t>
-  </si>
-  <si>
-    <t>18.923mm</t>
-  </si>
-  <si>
-    <t>9.454mm</t>
-  </si>
-  <si>
-    <t>UNIQUEX3</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>MX128-5.0-04P-GN01-Cu-Y-A</t>
-  </si>
-  <si>
-    <t>CONN-TH_4P-MX128-5.0-04P-GN01-CU-Y-A</t>
-  </si>
-  <si>
-    <t>16.315mm</t>
-  </si>
-  <si>
-    <t>18.288mm</t>
-  </si>
-  <si>
-    <t>10.788mm</t>
-  </si>
-  <si>
-    <t>1x4P 5mm 直插 排数:1 每排P数:4</t>
-  </si>
-  <si>
-    <t>C5290369</t>
-  </si>
-  <si>
-    <t>MAX(迈旭)</t>
-  </si>
-  <si>
-    <t>插件,P=5mm</t>
-  </si>
-  <si>
-    <t>gge1</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>31.242mm</t>
-  </si>
-  <si>
-    <t>6.309mm</t>
-  </si>
-  <si>
-    <t>UNIQUED2_1</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>MX128-5.0-06P-GN01-Cu-Y-A</t>
-  </si>
-  <si>
-    <t>CONN-TH_6P-P5.00_MX128-5.0-06P-GN01-CU-Y-A</t>
-  </si>
-  <si>
     <t>-24.692mm</t>
   </si>
   <si>
@@ -1442,6 +1445,45 @@
   </si>
   <si>
     <t>UNIQUER21</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>-15.377mm</t>
+  </si>
+  <si>
+    <t>-19.657mm</t>
+  </si>
+  <si>
+    <t>-20.657mm</t>
+  </si>
+  <si>
+    <t>UNIQUER4_1</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>-17.526mm</t>
+  </si>
+  <si>
+    <t>-19.685mm</t>
+  </si>
+  <si>
+    <t>-20.685mm</t>
+  </si>
+  <si>
+    <t>UNIQUER4_2</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>-25.638mm</t>
+  </si>
+  <si>
+    <t>UNIQUER4_3</t>
   </si>
 </sst>
 </file>
@@ -1818,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U59"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="21" width="20" customWidth="1"/>
@@ -2692,10 +2734,10 @@
         <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -2704,7 +2746,7 @@
         <v>28</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M14" t="s">
         <v>29</v>
@@ -2745,22 +2787,22 @@
         <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
+        <v>115</v>
+      </c>
+      <c r="F15" t="s">
         <v>114</v>
       </c>
-      <c r="F15" t="s">
-        <v>93</v>
-      </c>
       <c r="G15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" t="s">
         <v>114</v>
       </c>
-      <c r="H15" t="s">
-        <v>93</v>
-      </c>
       <c r="I15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J15">
         <v>2</v>
@@ -2778,13 +2820,13 @@
         <v>112</v>
       </c>
       <c r="O15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R15" t="s">
         <v>112</v>
@@ -2796,36 +2838,36 @@
         <v>34</v>
       </c>
       <c r="U15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" t="s">
         <v>124</v>
       </c>
-      <c r="F16" t="s">
-        <v>123</v>
-      </c>
       <c r="G16" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J16">
         <v>16</v>
@@ -2837,22 +2879,22 @@
         <v>180</v>
       </c>
       <c r="M16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S16" t="s">
         <v>12</v>
@@ -2861,36 +2903,36 @@
         <v>34</v>
       </c>
       <c r="U16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" t="s">
         <v>135</v>
       </c>
-      <c r="F17" t="s">
-        <v>134</v>
-      </c>
       <c r="G17" t="s">
+        <v>136</v>
+      </c>
+      <c r="H17" t="s">
         <v>135</v>
       </c>
-      <c r="H17" t="s">
-        <v>134</v>
-      </c>
       <c r="I17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J17">
         <v>2</v>
@@ -2905,19 +2947,19 @@
         <v>29</v>
       </c>
       <c r="N17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S17" t="s">
         <v>46</v>
@@ -2926,36 +2968,36 @@
         <v>34</v>
       </c>
       <c r="U17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -2970,19 +3012,19 @@
         <v>29</v>
       </c>
       <c r="N18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S18" t="s">
         <v>46</v>
@@ -2991,36 +3033,36 @@
         <v>34</v>
       </c>
       <c r="U18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E19" t="s">
+        <v>149</v>
+      </c>
+      <c r="F19" t="s">
         <v>148</v>
       </c>
-      <c r="F19" t="s">
-        <v>147</v>
-      </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J19">
         <v>6</v>
@@ -3032,60 +3074,60 @@
         <v>270</v>
       </c>
       <c r="M19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R19" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="T19" t="s">
         <v>34</v>
       </c>
       <c r="U19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20" t="s">
+        <v>161</v>
+      </c>
+      <c r="F20" t="s">
         <v>160</v>
       </c>
-      <c r="F20" t="s">
-        <v>159</v>
-      </c>
       <c r="G20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J20">
         <v>29</v>
@@ -3100,33 +3142,33 @@
         <v>29</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T20" t="s">
         <v>34</v>
       </c>
       <c r="U20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
         <v>37</v>
@@ -3135,22 +3177,22 @@
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F21" t="s">
         <v>169</v>
       </c>
-      <c r="F21" t="s">
-        <v>168</v>
-      </c>
       <c r="G21" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H21" t="s">
+        <v>171</v>
+      </c>
+      <c r="I21" t="s">
         <v>170</v>
-      </c>
-      <c r="I21" t="s">
-        <v>169</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -3186,12 +3228,12 @@
         <v>34</v>
       </c>
       <c r="U21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
@@ -3200,22 +3242,22 @@
         <v>38</v>
       </c>
       <c r="D22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22" t="s">
         <v>174</v>
       </c>
-      <c r="F22" t="s">
-        <v>173</v>
-      </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H22" t="s">
+        <v>176</v>
+      </c>
+      <c r="I22" t="s">
         <v>175</v>
-      </c>
-      <c r="I22" t="s">
-        <v>174</v>
       </c>
       <c r="J22">
         <v>2</v>
@@ -3251,36 +3293,36 @@
         <v>34</v>
       </c>
       <c r="U22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E23" t="s">
+        <v>182</v>
+      </c>
+      <c r="F23" t="s">
         <v>181</v>
       </c>
-      <c r="F23" t="s">
-        <v>180</v>
-      </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I23" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J23">
         <v>45</v>
@@ -3295,57 +3337,57 @@
         <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P23" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="Q23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="S23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T23" t="s">
         <v>34</v>
       </c>
       <c r="U23" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B24" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C24" t="s">
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E24" t="s">
+        <v>191</v>
+      </c>
+      <c r="F24" t="s">
         <v>190</v>
       </c>
-      <c r="F24" t="s">
-        <v>189</v>
-      </c>
       <c r="G24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H24" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" t="s">
         <v>191</v>
-      </c>
-      <c r="I24" t="s">
-        <v>190</v>
       </c>
       <c r="J24">
         <v>2</v>
@@ -3360,19 +3402,19 @@
         <v>29</v>
       </c>
       <c r="N24" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O24" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P24" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q24" t="s">
         <v>45</v>
       </c>
       <c r="R24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S24" t="s">
         <v>46</v>
@@ -3381,36 +3423,36 @@
         <v>34</v>
       </c>
       <c r="U24" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B25" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
         <v>199</v>
       </c>
-      <c r="F25" t="s">
-        <v>198</v>
-      </c>
       <c r="G25" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="H25" t="s">
         <v>200</v>
       </c>
       <c r="I25" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="J25">
         <v>2</v>
@@ -3425,19 +3467,19 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q25" t="s">
         <v>45</v>
       </c>
       <c r="R25" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="S25" t="s">
         <v>46</v>
@@ -3487,7 +3529,7 @@
         <v>180</v>
       </c>
       <c r="M26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N26" t="s">
         <v>203</v>
@@ -3525,22 +3567,22 @@
         <v>216</v>
       </c>
       <c r="D27" t="s">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="E27" t="s">
+        <v>218</v>
+      </c>
+      <c r="F27" t="s">
         <v>217</v>
       </c>
-      <c r="F27" t="s">
-        <v>102</v>
-      </c>
       <c r="G27" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" t="s">
         <v>217</v>
       </c>
-      <c r="H27" t="s">
-        <v>102</v>
-      </c>
       <c r="I27" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J27">
         <v>2</v>
@@ -3558,54 +3600,54 @@
         <v>215</v>
       </c>
       <c r="O27" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P27" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q27" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R27" t="s">
         <v>215</v>
       </c>
       <c r="S27" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="T27" t="s">
         <v>34</v>
       </c>
       <c r="U27" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" t="s">
         <v>60</v>
       </c>
       <c r="D28" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E28" t="s">
+        <v>228</v>
+      </c>
+      <c r="F28" t="s">
         <v>227</v>
       </c>
-      <c r="F28" t="s">
-        <v>226</v>
-      </c>
       <c r="G28" t="s">
+        <v>228</v>
+      </c>
+      <c r="H28" t="s">
         <v>227</v>
       </c>
-      <c r="H28" t="s">
-        <v>226</v>
-      </c>
       <c r="I28" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -3620,19 +3662,19 @@
         <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O28" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P28" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q28" t="s">
         <v>108</v>
       </c>
       <c r="R28" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S28" t="s">
         <v>46</v>
@@ -3641,33 +3683,33 @@
         <v>109</v>
       </c>
       <c r="U28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
         <v>60</v>
       </c>
       <c r="D29" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="E29" t="s">
         <v>235</v>
       </c>
       <c r="F29" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="G29" t="s">
         <v>235</v>
       </c>
       <c r="H29" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="I29" t="s">
         <v>236</v>
@@ -3685,19 +3727,19 @@
         <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="O29" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P29" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q29" t="s">
         <v>108</v>
       </c>
       <c r="R29" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S29" t="s">
         <v>46</v>
@@ -3824,7 +3866,7 @@
         <v>255</v>
       </c>
       <c r="Q31" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R31" t="s">
         <v>249</v>
@@ -3889,7 +3931,7 @@
         <v>255</v>
       </c>
       <c r="Q32" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R32" t="s">
         <v>249</v>
@@ -4370,19 +4412,19 @@
         <v>60</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="E40" t="s">
         <v>325</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="G40" t="s">
         <v>325</v>
       </c>
       <c r="H40" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="I40" t="s">
         <v>326</v>
@@ -4435,19 +4477,19 @@
         <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E41" t="s">
         <v>332</v>
       </c>
       <c r="F41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G41" t="s">
         <v>332</v>
       </c>
       <c r="H41" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I41" t="s">
         <v>333</v>
@@ -4864,7 +4906,7 @@
         <v>381</v>
       </c>
       <c r="Q47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="R47" t="s">
         <v>375</v>
@@ -4955,22 +4997,22 @@
         <v>395</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H49" t="s">
         <v>396</v>
       </c>
       <c r="I49" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J49">
         <v>3</v>
@@ -5112,7 +5154,7 @@
         <v>90</v>
       </c>
       <c r="M51" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N51" t="s">
         <v>409</v>
@@ -5215,22 +5257,22 @@
         <v>425</v>
       </c>
       <c r="D53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E53" t="s">
-        <v>198</v>
+        <v>426</v>
       </c>
       <c r="F53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G53" t="s">
-        <v>198</v>
+        <v>426</v>
       </c>
       <c r="H53" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I53" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J53">
         <v>6</v>
@@ -5242,16 +5284,16 @@
         <v>90</v>
       </c>
       <c r="M53" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N53" t="s">
         <v>424</v>
       </c>
       <c r="O53" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P53" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q53" t="s">
         <v>416</v>
@@ -5266,36 +5308,36 @@
         <v>34</v>
       </c>
       <c r="U53" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B54" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C54" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D54" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E54" t="s">
+        <v>435</v>
+      </c>
+      <c r="F54" t="s">
         <v>434</v>
       </c>
-      <c r="F54" t="s">
-        <v>433</v>
-      </c>
       <c r="G54" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H54" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I54" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -5310,33 +5352,33 @@
         <v>29</v>
       </c>
       <c r="N54" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O54" t="s">
+        <v>439</v>
+      </c>
+      <c r="P54" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>441</v>
+      </c>
+      <c r="R54" t="s">
         <v>438</v>
       </c>
-      <c r="P54" t="s">
-        <v>439</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>440</v>
-      </c>
-      <c r="R54" t="s">
-        <v>437</v>
-      </c>
       <c r="S54" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="T54" t="s">
         <v>34</v>
       </c>
       <c r="U54" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s">
         <v>239</v>
@@ -5345,22 +5387,22 @@
         <v>38</v>
       </c>
       <c r="D55" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E55" t="s">
+        <v>446</v>
+      </c>
+      <c r="F55" t="s">
         <v>445</v>
       </c>
-      <c r="F55" t="s">
-        <v>444</v>
-      </c>
       <c r="G55" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H55" t="s">
+        <v>447</v>
+      </c>
+      <c r="I55" t="s">
         <v>446</v>
-      </c>
-      <c r="I55" t="s">
-        <v>445</v>
       </c>
       <c r="J55">
         <v>2</v>
@@ -5396,36 +5438,36 @@
         <v>34</v>
       </c>
       <c r="U55" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B56" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C56" t="s">
         <v>38</v>
       </c>
       <c r="D56" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E56" t="s">
+        <v>452</v>
+      </c>
+      <c r="F56" t="s">
         <v>451</v>
       </c>
-      <c r="F56" t="s">
-        <v>450</v>
-      </c>
       <c r="G56" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H56" t="s">
+        <v>453</v>
+      </c>
+      <c r="I56" t="s">
         <v>452</v>
-      </c>
-      <c r="I56" t="s">
-        <v>451</v>
       </c>
       <c r="J56">
         <v>2</v>
@@ -5440,19 +5482,19 @@
         <v>29</v>
       </c>
       <c r="N56" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O56" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P56" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q56" t="s">
         <v>246</v>
       </c>
       <c r="R56" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="S56" t="s">
         <v>46</v>
@@ -5461,12 +5503,12 @@
         <v>34</v>
       </c>
       <c r="U56" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B57" t="s">
         <v>37</v>
@@ -5475,22 +5517,22 @@
         <v>38</v>
       </c>
       <c r="D57" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E57" t="s">
+        <v>460</v>
+      </c>
+      <c r="F57" t="s">
         <v>459</v>
       </c>
-      <c r="F57" t="s">
-        <v>458</v>
-      </c>
       <c r="G57" t="s">
+        <v>460</v>
+      </c>
+      <c r="H57" t="s">
         <v>459</v>
       </c>
-      <c r="H57" t="s">
-        <v>458</v>
-      </c>
       <c r="I57" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J57">
         <v>2</v>
@@ -5526,12 +5568,12 @@
         <v>34</v>
       </c>
       <c r="U57" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B58" t="s">
         <v>101</v>
@@ -5540,22 +5582,22 @@
         <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E58" t="s">
+        <v>465</v>
+      </c>
+      <c r="F58" t="s">
         <v>464</v>
       </c>
-      <c r="F58" t="s">
-        <v>463</v>
-      </c>
       <c r="G58" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H58" t="s">
+        <v>466</v>
+      </c>
+      <c r="I58" t="s">
         <v>465</v>
-      </c>
-      <c r="I58" t="s">
-        <v>464</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -5591,36 +5633,36 @@
         <v>109</v>
       </c>
       <c r="U58" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B59" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C59" t="s">
         <v>60</v>
       </c>
       <c r="D59" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E59" t="s">
+        <v>471</v>
+      </c>
+      <c r="F59" t="s">
         <v>470</v>
       </c>
-      <c r="F59" t="s">
-        <v>469</v>
-      </c>
       <c r="G59" t="s">
+        <v>471</v>
+      </c>
+      <c r="H59" t="s">
         <v>470</v>
       </c>
-      <c r="H59" t="s">
-        <v>469</v>
-      </c>
       <c r="I59" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J59">
         <v>2</v>
@@ -5635,19 +5677,19 @@
         <v>29</v>
       </c>
       <c r="N59" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O59" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P59" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q59" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R59" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="S59" t="s">
         <v>46</v>
@@ -5656,7 +5698,202 @@
         <v>34</v>
       </c>
       <c r="U59" t="s">
-        <v>476</v>
+        <v>477</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>478</v>
+      </c>
+      <c r="B60" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>479</v>
+      </c>
+      <c r="E60" t="s">
+        <v>480</v>
+      </c>
+      <c r="F60" t="s">
+        <v>479</v>
+      </c>
+      <c r="G60" t="s">
+        <v>480</v>
+      </c>
+      <c r="H60" t="s">
+        <v>479</v>
+      </c>
+      <c r="I60" t="s">
+        <v>481</v>
+      </c>
+      <c r="J60">
+        <v>2</v>
+      </c>
+      <c r="K60" t="s">
+        <v>28</v>
+      </c>
+      <c r="L60">
+        <v>90</v>
+      </c>
+      <c r="M60" t="s">
+        <v>29</v>
+      </c>
+      <c r="N60" t="s">
+        <v>105</v>
+      </c>
+      <c r="O60" t="s">
+        <v>106</v>
+      </c>
+      <c r="P60" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>108</v>
+      </c>
+      <c r="R60" t="s">
+        <v>101</v>
+      </c>
+      <c r="S60" t="s">
+        <v>46</v>
+      </c>
+      <c r="T60" t="s">
+        <v>109</v>
+      </c>
+      <c r="U60" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s">
+        <v>101</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>484</v>
+      </c>
+      <c r="E61" t="s">
+        <v>485</v>
+      </c>
+      <c r="F61" t="s">
+        <v>484</v>
+      </c>
+      <c r="G61" t="s">
+        <v>485</v>
+      </c>
+      <c r="H61" t="s">
+        <v>484</v>
+      </c>
+      <c r="I61" t="s">
+        <v>486</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61" t="s">
+        <v>28</v>
+      </c>
+      <c r="L61">
+        <v>90</v>
+      </c>
+      <c r="M61" t="s">
+        <v>29</v>
+      </c>
+      <c r="N61" t="s">
+        <v>105</v>
+      </c>
+      <c r="O61" t="s">
+        <v>106</v>
+      </c>
+      <c r="P61" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>108</v>
+      </c>
+      <c r="R61" t="s">
+        <v>101</v>
+      </c>
+      <c r="S61" t="s">
+        <v>46</v>
+      </c>
+      <c r="T61" t="s">
+        <v>109</v>
+      </c>
+      <c r="U61" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>101</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>70</v>
+      </c>
+      <c r="E62" t="s">
+        <v>208</v>
+      </c>
+      <c r="F62" t="s">
+        <v>70</v>
+      </c>
+      <c r="G62" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" t="s">
+        <v>70</v>
+      </c>
+      <c r="I62" t="s">
+        <v>489</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" t="s">
+        <v>28</v>
+      </c>
+      <c r="L62">
+        <v>90</v>
+      </c>
+      <c r="M62" t="s">
+        <v>29</v>
+      </c>
+      <c r="N62" t="s">
+        <v>105</v>
+      </c>
+      <c r="O62" t="s">
+        <v>106</v>
+      </c>
+      <c r="P62" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>108</v>
+      </c>
+      <c r="R62" t="s">
+        <v>101</v>
+      </c>
+      <c r="S62" t="s">
+        <v>46</v>
+      </c>
+      <c r="T62" t="s">
+        <v>109</v>
+      </c>
+      <c r="U62" t="s">
+        <v>490</v>
       </c>
     </row>
   </sheetData>
